--- a/data/test/data.xlsx
+++ b/data/test/data.xlsx
@@ -79,12 +79,18 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFD095"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -121,13 +127,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -143,6 +157,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFAFD095"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -257,41 +331,45 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
-  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AMJ124"/>
+  <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="21.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="49.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1023" style="1" width="11.52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="3" customFormat="true" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AMI1" s="2"/>
+      <c r="AMJ1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -308,7 +386,7 @@
       </c>
       <c r="E2" s="1" t="str">
         <f aca="true">"test" &amp; ROW(E1) &amp; "-" &amp; TEXT(TODAY(),"aaaa-mm-jj") &amp; "@test.com"</f>
-        <v>test1-2024-10-23@test.com</v>
+        <v>test1-2024-10-24@test.com</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>611223344</v>
@@ -318,11 +396,11 @@
         <v>test message 1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="1" t="str">
@@ -335,7 +413,7 @@
       </c>
       <c r="E3" s="1" t="str">
         <f aca="true">"test" &amp; ROW(E2) &amp; "-" &amp; TEXT(TODAY(),"aaaa-mm-jj") &amp; "@test.com"</f>
-        <v>test2-2024-10-23@test.com</v>
+        <v>test2-2024-10-24@test.com</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>622334455</v>
@@ -345,11 +423,11 @@
         <v>test message 2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="1" t="str">
@@ -362,7 +440,7 @@
       </c>
       <c r="E4" s="1" t="str">
         <f aca="true">"test" &amp; ROW(E3) &amp; "-" &amp; TEXT(TODAY(),"aaaa-mm-jj") &amp; "@test.com"</f>
-        <v>test3-2024-10-23@test.com</v>
+        <v>test3-2024-10-24@test.com</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>633445566</v>
@@ -372,236 +450,236 @@
         <v>test message 3</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2"/>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2"/>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2"/>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2"/>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2"/>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2"/>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2"/>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2"/>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2"/>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2"/>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2"/>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2"/>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2"/>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2"/>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2"/>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2"/>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2"/>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2"/>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2"/>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2"/>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2"/>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2"/>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2"/>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2"/>
-    </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2"/>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="2"/>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2"/>
-    </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2"/>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2"/>
-    </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2"/>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2"/>
+    <row r="13" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4"/>
+    </row>
+    <row r="29" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4"/>
+    </row>
+    <row r="38" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4"/>
+    </row>
+    <row r="41" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4"/>
+    </row>
+    <row r="43" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4"/>
+    </row>
+    <row r="44" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4"/>
+    </row>
+    <row r="45" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4"/>
+    </row>
+    <row r="49" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4"/>
+    </row>
+    <row r="50" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4"/>
+    </row>
+    <row r="51" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4"/>
+    </row>
+    <row r="53" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4"/>
+    </row>
+    <row r="54" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4"/>
+    </row>
+    <row r="58" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4"/>
+    </row>
+    <row r="59" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4"/>
+    </row>
+    <row r="61" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4"/>
+    </row>
+    <row r="71" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4"/>
+    </row>
+    <row r="73" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4"/>
+    </row>
+    <row r="74" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4"/>
+    </row>
+    <row r="75" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4"/>
+    </row>
+    <row r="78" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4"/>
+    </row>
+    <row r="79" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4"/>
+    </row>
+    <row r="80" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4"/>
+    </row>
+    <row r="81" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4"/>
+    </row>
+    <row r="83" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4"/>
+    </row>
+    <row r="85" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4"/>
+    </row>
+    <row r="88" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4"/>
+    </row>
+    <row r="89" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4"/>
+    </row>
+    <row r="90" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4"/>
+    </row>
+    <row r="91" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4"/>
+    </row>
+    <row r="93" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4"/>
+    </row>
+    <row r="94" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4"/>
+    </row>
+    <row r="95" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4"/>
+    </row>
+    <row r="98" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4"/>
+    </row>
+    <row r="99" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4"/>
+    </row>
+    <row r="100" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4"/>
+    </row>
+    <row r="101" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4"/>
+    </row>
+    <row r="103" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4"/>
+    </row>
+    <row r="104" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4"/>
+    </row>
+    <row r="105" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4"/>
+    </row>
+    <row r="110" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4"/>
+    </row>
+    <row r="116" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4"/>
+    </row>
+    <row r="117" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4"/>
+    </row>
+    <row r="118" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4"/>
+    </row>
+    <row r="121" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4"/>
+    </row>
+    <row r="122" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4"/>
+    </row>
+    <row r="123" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4"/>
+    </row>
+    <row r="124" customFormat="false" ht="21.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/data/test/data.xlsx
+++ b/data/test/data.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="welcome_front" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="test" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -140,7 +140,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -334,11 +334,11 @@
   <dimension ref="A1:AMJ124"/>
   <sheetFormatPr defaultColWidth="12.390625" defaultRowHeight="21.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1023" style="1" width="11.52"/>
@@ -386,7 +386,7 @@
       </c>
       <c r="E2" s="1" t="str">
         <f aca="true">"test" &amp; ROW(E1) &amp; "-" &amp; TEXT(TODAY(),"aaaa-mm-jj") &amp; "@test.com"</f>
-        <v>test1-2024-10-24@test.com</v>
+        <v>test1-2024-11-04@test.com</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>611223344</v>
@@ -413,7 +413,7 @@
       </c>
       <c r="E3" s="1" t="str">
         <f aca="true">"test" &amp; ROW(E2) &amp; "-" &amp; TEXT(TODAY(),"aaaa-mm-jj") &amp; "@test.com"</f>
-        <v>test2-2024-10-24@test.com</v>
+        <v>test2-2024-11-04@test.com</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>622334455</v>
@@ -440,7 +440,7 @@
       </c>
       <c r="E4" s="1" t="str">
         <f aca="true">"test" &amp; ROW(E3) &amp; "-" &amp; TEXT(TODAY(),"aaaa-mm-jj") &amp; "@test.com"</f>
-        <v>test3-2024-10-24@test.com</v>
+        <v>test3-2024-11-04@test.com</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>633445566</v>
